--- a/product_selector_out/STM32F100 value Line.xlsx
+++ b/product_selector_out/STM32F100 value Line.xlsx
@@ -7931,9 +7931,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA12" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB12" s="9" t="inlineStr">
@@ -8258,9 +8258,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA13" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB13" s="9" t="inlineStr">
@@ -8585,9 +8585,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA14" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB14" s="9" t="inlineStr">
@@ -8912,9 +8912,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA15" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB15" s="9" t="inlineStr">
@@ -9239,9 +9239,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA16" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB16" s="9" t="inlineStr">
@@ -9566,9 +9566,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA17" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB17" s="9" t="inlineStr">
@@ -9893,9 +9893,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA18" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB18" s="9" t="inlineStr">
@@ -10220,9 +10220,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA19" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB19" s="9" t="inlineStr">
@@ -10547,9 +10547,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA20" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB20" s="9" t="inlineStr">
@@ -10874,9 +10874,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA21" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB21" s="9" t="inlineStr">
@@ -11201,9 +11201,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA22" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB22" s="9" t="inlineStr">
@@ -11528,9 +11528,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA23" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB23" s="9" t="inlineStr">
@@ -11583,9 +11583,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL23" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM23" s="9" t="inlineStr">
@@ -11855,9 +11855,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA24" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB24" s="9" t="inlineStr">
@@ -12182,9 +12182,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA25" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB25" s="9" t="inlineStr">
@@ -12237,9 +12237,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL25" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM25" s="9" t="inlineStr">
@@ -12509,9 +12509,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA26" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB26" s="9" t="inlineStr">
@@ -12836,9 +12836,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA27" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB27" s="9" t="inlineStr">
@@ -13163,9 +13163,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA28" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB28" s="9" t="inlineStr">
@@ -13490,9 +13490,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA29" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB29" s="9" t="inlineStr">
@@ -13817,9 +13817,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA30" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA30" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB30" s="9" t="inlineStr">

--- a/product_selector_out/STM32F100 value Line.xlsx
+++ b/product_selector_out/STM32F100 value Line.xlsx
@@ -7991,9 +7991,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM12" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN12" s="9" t="inlineStr">
@@ -8645,9 +8645,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM14" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN14" s="9" t="inlineStr">
@@ -9299,9 +9299,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM16" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN16" s="9" t="inlineStr">
@@ -10607,9 +10607,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM20" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN20" s="9" t="inlineStr">
@@ -10934,9 +10934,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM21" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN21" s="9" t="inlineStr">
@@ -11261,9 +11261,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM22" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN22" s="9" t="inlineStr">
@@ -13223,9 +13223,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM28" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN28" s="9" t="inlineStr">
@@ -13550,9 +13550,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM29" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN29" s="9" t="inlineStr">
@@ -13877,9 +13877,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM30" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM30" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN30" s="9" t="inlineStr">

--- a/product_selector_out/STM32F100 value Line.xlsx
+++ b/product_selector_out/STM32F100 value Line.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM30"/>
+  <dimension ref="A1:BN30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.51953125" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,8 @@
     <col width="21.765625" customWidth="1" min="62" max="62"/>
     <col width="18" customWidth="1" min="63" max="63"/>
     <col width="18" customWidth="1" min="64" max="64"/>
-    <col width="52" customWidth="1" min="65" max="65"/>
+    <col width="18" customWidth="1" min="65" max="65"/>
+    <col width="52" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -895,6 +896,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -990,6 +996,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1314,6 +1321,11 @@
       </c>
       <c r="BM12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f100rc.pdf</t>
         </is>
       </c>
@@ -1641,6 +1653,11 @@
       </c>
       <c r="BM13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f100c4.pdf</t>
         </is>
       </c>
@@ -1968,6 +1985,11 @@
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f100rc.pdf</t>
         </is>
       </c>
@@ -2295,6 +2317,11 @@
       </c>
       <c r="BM15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f100c4.pdf</t>
         </is>
       </c>
@@ -2622,6 +2649,11 @@
       </c>
       <c r="BM16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f100rc.pdf</t>
         </is>
       </c>
@@ -2949,6 +2981,11 @@
       </c>
       <c r="BM17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f100c4.pdf</t>
         </is>
       </c>
@@ -3276,6 +3313,11 @@
       </c>
       <c r="BM18" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f100c4.pdf</t>
         </is>
       </c>
@@ -3603,6 +3645,11 @@
       </c>
       <c r="BM19" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f100c4.pdf</t>
         </is>
       </c>
@@ -3930,6 +3977,11 @@
       </c>
       <c r="BM20" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f100rc.pdf</t>
         </is>
       </c>
@@ -4257,6 +4309,11 @@
       </c>
       <c r="BM21" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN21" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f100rc.pdf</t>
         </is>
       </c>
@@ -4584,6 +4641,11 @@
       </c>
       <c r="BM22" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN22" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f100rc.pdf</t>
         </is>
       </c>
@@ -4911,6 +4973,11 @@
       </c>
       <c r="BM23" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN23" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f100c4.pdf</t>
         </is>
       </c>
@@ -5238,6 +5305,11 @@
       </c>
       <c r="BM24" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN24" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f100c4.pdf</t>
         </is>
       </c>
@@ -5565,6 +5637,11 @@
       </c>
       <c r="BM25" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN25" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f100c4.pdf</t>
         </is>
       </c>
@@ -5892,6 +5969,11 @@
       </c>
       <c r="BM26" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN26" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f100c4.pdf</t>
         </is>
       </c>
@@ -6219,6 +6301,11 @@
       </c>
       <c r="BM27" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN27" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f100c4.pdf</t>
         </is>
       </c>
@@ -6546,6 +6633,11 @@
       </c>
       <c r="BM28" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN28" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f100rc.pdf</t>
         </is>
       </c>
@@ -6873,6 +6965,11 @@
       </c>
       <c r="BM29" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN29" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f100rc.pdf</t>
         </is>
       </c>
@@ -7200,12 +7297,17 @@
       </c>
       <c r="BM30" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN30" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f100rc.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="64">
+  <mergeCells count="65">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -7226,16 +7328,14 @@
     <mergeCell ref="BA10:BA11"/>
     <mergeCell ref="BG10:BG11"/>
     <mergeCell ref="Q10:Q11"/>
-    <mergeCell ref="A1:BM8"/>
     <mergeCell ref="AR10:AR11"/>
+    <mergeCell ref="AT10:AT11"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="BI10:BI11"/>
     <mergeCell ref="AV10:AV11"/>
-    <mergeCell ref="A9:BM9"/>
     <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -7248,6 +7348,7 @@
     <mergeCell ref="AQ10:AQ11"/>
     <mergeCell ref="AW10:AW11"/>
     <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
     <mergeCell ref="BK10:BK11"/>
     <mergeCell ref="A10:A11"/>
@@ -7267,7 +7368,9 @@
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="AG10:AG11"/>
     <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A9:BN9"/>
     <mergeCell ref="H10:H11"/>
+    <mergeCell ref="A1:BN8"/>
     <mergeCell ref="T10:T11"/>
     <mergeCell ref="J10:J11"/>
   </mergeCells>
@@ -7303,7 +7406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM30"/>
+  <dimension ref="A1:BN30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7371,6 +7474,7 @@
     <col width="16" customWidth="1" min="63" max="63"/>
     <col width="16" customWidth="1" min="64" max="64"/>
     <col width="16" customWidth="1" min="65" max="65"/>
+    <col width="16" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7704,6 +7808,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -7799,6 +7908,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -8121,7 +8231,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM12" s="6" t="inlineStr">
+      <c r="BM12" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8448,7 +8563,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM13" s="6" t="inlineStr">
+      <c r="BM13" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8775,7 +8895,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM14" s="6" t="inlineStr">
+      <c r="BM14" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9102,7 +9227,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM15" s="6" t="inlineStr">
+      <c r="BM15" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9429,7 +9559,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM16" s="6" t="inlineStr">
+      <c r="BM16" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9756,7 +9891,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM17" s="6" t="inlineStr">
+      <c r="BM17" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10083,7 +10223,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM18" s="6" t="inlineStr">
+      <c r="BM18" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10410,7 +10555,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM19" s="6" t="inlineStr">
+      <c r="BM19" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10737,7 +10887,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM20" s="6" t="inlineStr">
+      <c r="BM20" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11064,7 +11219,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM21" s="6" t="inlineStr">
+      <c r="BM21" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN21" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11391,7 +11551,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM22" s="6" t="inlineStr">
+      <c r="BM22" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN22" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11718,7 +11883,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM23" s="6" t="inlineStr">
+      <c r="BM23" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN23" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12045,7 +12215,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM24" s="6" t="inlineStr">
+      <c r="BM24" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN24" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12372,7 +12547,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM25" s="6" t="inlineStr">
+      <c r="BM25" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN25" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12699,7 +12879,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM26" s="6" t="inlineStr">
+      <c r="BM26" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN26" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13026,7 +13211,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM27" s="6" t="inlineStr">
+      <c r="BM27" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN27" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13353,7 +13543,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM28" s="6" t="inlineStr">
+      <c r="BM28" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN28" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13680,7 +13875,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM29" s="6" t="inlineStr">
+      <c r="BM29" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN29" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14007,7 +14207,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM30" s="6" t="inlineStr">
+      <c r="BM30" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN30" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14015,8 +14220,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BM9"/>
-    <mergeCell ref="A1:BM8"/>
+    <mergeCell ref="A9:BN9"/>
+    <mergeCell ref="A1:BN8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
